--- a/hira_material_automation/output/monthly/202601_202606__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__temporary_synovial_substitute__250099__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:23:40</t>
+          <t>2026-06-14T22:17:01</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5b86132c246a751d5095278fb0df9cd9a26c66344757ba48561e6df13f2d4547</t>
+          <t>eaea84c6f5d1df11c0cea0d4be3dd266267130dcace06ff8569001756a0aa5e3</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__temporary_synovial_substitute__250099__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:01</t>
+          <t>2026-06-24T22:21:47</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eaea84c6f5d1df11c0cea0d4be3dd266267130dcace06ff8569001756a0aa5e3</t>
+          <t>a104d727ef735c04f8ff61f8d2df820c336a9ecea54f0179f21de0e0b2286a28</t>
         </is>
       </c>
     </row>
